--- a/Forkin-finding-2014-gemma3.xlsx
+++ b/Forkin-finding-2014-gemma3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t>DOCUMENT</t>
   </si>
@@ -64,6 +64,18 @@
     <t>Summarize the coroner’s findings in 2-3 sentences</t>
   </si>
   <si>
+    <t>Did the coroner make recommendations for future prevention? If yes, what were they?</t>
+  </si>
+  <si>
+    <t>Differentiate between the immediate cause of death and contributing factors.</t>
+  </si>
+  <si>
+    <t>Did the coroner evaluate the adequacy of supervision, treatment, or care provided? Explain the conclusion.</t>
+  </si>
+  <si>
+    <t>Does this case highlight any broader patterns or lessons relevant to public safety or institutional care?</t>
+  </si>
+  <si>
     <t>The deceased was Luke Isaac Forkin, born in Western Australia on 23 October 1982 (page 4)</t>
   </si>
   <si>
@@ -97,7 +109,19 @@
     <t>The coroner found that Luke Forkin committed suicide by hanging while absent without leave from Graylands Hospital. The care, treatment, and supervision were reasonable and appropriate, and the decision to grant unescorted ground access was justified by his apparent stability (pages 20–21).</t>
   </si>
   <si>
-    <t>Based on the provided context, the deceased was a man born in Western Australia in 1982 into a blended family. He had a complex family history including a biological father in prison, a mother with three partners, and a challenging adolescence marked by drug use, criminal activity, and difficulties fitting in socially. He experienced a serious injury in 2002 resulting in a disability pension and substantial compensation.</t>
+    <t>Yes. The coroner noted that Dr. Nathan Gibson (Chief Psychiatrist) had initiated development of a Mental Health Act orientation and training program for all consultant psychiatrists to clarify the legal requirements for detaining and treating patients with personality disorders (page 20).</t>
+  </si>
+  <si>
+    <t>Immediate cause: Ligature compression of the neck (hanging) (page 14). Contributing factors: Substance abuse, personality disorder, pending court case, strained relationship with his mother, and recent absconding from psychiatric care (pages 9–13, 20)</t>
+  </si>
+  <si>
+    <t>Yes. The coroner concluded that Graylands Hospital staff provided reasonable and appropriate treatment and supervision. Although there were minor issues with record-keeping and a 45-minute delay in declaring him AWOL, these were not contributory to the death. Staff acted under the “least restrictive” principle of care (pages 15–17).</t>
+  </si>
+  <si>
+    <t>Yes. The case highlights the complex challenges in managing patients with personality and substance-use disorders and the need for clearer guidance under the Mental Health Act. It also emphasized system improvements in record-keeping, risk assessment, and staff training, which were implemented after the inquest (pages 18–20)</t>
+  </si>
+  <si>
+    <t>Based on the provided context, the deceased was a man born in Western Australia in 1982 into a blended family. He experienced a challenging life marked by difficulties fitting in socially, a history of drug use (including amphetamines, cannabis, heroin, LSD, and ecstasy), criminal activity (burglary and drug-related offenses), and a serious injury sustained in a shooting involving his step-father. He received the Disability Support Pension following the injury and led an itinerant lifestyle.</t>
   </si>
   <si>
     <t>29 November 2010</t>
@@ -113,39 +137,69 @@
   </si>
   <si>
     <t>Here’s a breakdown of the circumstances leading to the death, based solely on the provided text:
-Mr. Ward and his wife returned home from work and found the deceased hanging by his neck with an electrical cord tied to a rafter through an open manhole. Mr. Ward immediately called 000, cut the electrical cord, and performed chest compressions until ambulance paramedics arrived. Despite their efforts, the deceased was not revived. A post-mortem examination revealed ligature compression of the neck (hanging), a fracture of the main throat cartilage, and congestion of the lungs consistent with asphyxiation. Toxicology analysis indicated the presence of prescription medications and a low level of tetrahydrocannabinol (cannabis). 
-**Key elements of the circumstances:**
-*   **Hanging:** The immediate cause of death was hanging with an electrical cord.
-*   **Drug Use:** The deceased had a long history of drug use, including amphetamines, cannabis, heroin, LSD, and ecstasy.
-*   **Initial Response:** Mr. Ward’s quick action in calling for help and performing CPR attempted to reverse the effects of the hanging.</t>
+Mr. Ward and his wife returned home from work to find the deceased hanging by his neck with an electrical cord tied to a rafter through an open manhole. Mr. Ward called 000, cut the electrical cord, and performed chest compressions until paramedics arrived. The paramedics were unable to revive him. A post-mortem examination revealed a ligature-type marking on the neck and internal neck injury with fracture of the main throat cartilage, consistent with asphyxiation due to neck compression. Toxicology analysis showed the presence of prescription medications and cannabis use within the 24 hours prior to death. The deceased had a history of drug use, including amphetamines, cannabis, heroin, LSD and ecstasy, and had a previous injury from a gunshot wound to the abdomen.</t>
   </si>
   <si>
     <t>Based on the provided context, the deceased had the following relevant medical and mental health history:
 *   **Schizophrenia:** Diagnosed in 2005 with psychotic symptoms.
 *   **Amphetamine-Induced Psychosis:** Diagnosed in 2006 following amphetamine use.
-*   **Suicidal Behaviour:** Attempted suicide in November 2007 involving self-harm with petrol.
-*   **Substance Abuse:** A history of amphetamine use, including intravenous use, which was a significant factor in his psychotic episodes.
-*   **Paranoid Psychotic Episodes:** Experienced exacerbated paranoid psychotic episodes due to substance abuse.
-*   **Suicidal Ideation:** Experienced suicidal ideation, particularly in 2007.</t>
+*   **Suicidal Ideation and Behavior:** Multiple instances of suicidal thoughts and attempts, including pouring petrol on himself and his car in 2007.
+*   **Substance Abuse:** A significant history of intravenous amphetamine use, which was a recurring factor in his mental health issues.
+*   **Paranoid Psychotic Episodes:** Experienced paranoid psychotic episodes exacerbated by substance abuse.
+*   **Mental Health Unit Admissions:** Multiple admissions to the Joondalup Mental Health Unit for treatment.</t>
   </si>
   <si>
     <t>Based on the provided text, the following individuals and groups testified or assisted in the inquest:
 *   **Coroner DH. Mulligan:** Initially conducted the inquest and provided evidence.
-*   **Acting State Coroner Evelyn Vicker:** Directed the investigation after Coroner Mulligan was unable to make findings.
-*   **Interested parties:** Those present at the inquests before Coroner Mulligan were invited to make fresh or further submissions, and they agreed with the procedure.
-*   **Witnesses providing evidence specific to the deceased:** (The text doesn’t specify who these individuals were, but they were central to the inquest’s proceedings).
-*   **Individuals providing evidence about Graylands:** Including those who provided evidence on the condition of the buildings.</t>
-  </si>
-  <si>
-    <t>Yes, the deceased, Luke Isaac Forkin, was considered a “person held in care” under the Coroners Act 1996. The text explicitly states: “As the deceased was an involuntary patient under the Mental Health Act 1996 at the time of his death, he was a ‘person held in care’ under section 3 of the Coroners Act 1996.”</t>
+*   **Acting State Coroner Evelyn Vicker:** Directed the inquest after Coroner Mulligan became unable to make findings.
+*   **Interested parties:** Those present at the inquests before Coroner Mulligan were invited to make fresh or further submissions, and they agreed with the new procedure.
+*   **Exhibit, material and transcript of audio recordings** provided for the inquest.</t>
+  </si>
+  <si>
+    <t>Yes, the deceased, Luke Isaac Forkin, was considered a “person held in care” under the Coroners Act 1996. The document states: “As the deceased was an involuntary patient under the Mental Health Act 1996 at the time of his death, he was a ‘person held in care’ under section 3 of the Coroners Act 1996.”</t>
   </si>
   <si>
     <t>Yes, there was evidence of substances and drugs in the body.
 **Summary of Toxicology Findings:**
-A toxicology analysis revealed therapeutic and sub-therapeutic levels of prescription medicines, a low level of tetrahydrocannabinol (indicating cannabis use within 24 hours), and evidence of intermittent use of heroin, LSD, and ecstasy.</t>
-  </si>
-  <si>
-    <t>The coroner addressed general issues related to Graylands Hospital’s systemic problems, primarily concerning supervision, treatment, and care of the deceased patients, as evidenced during the inquest. However, the coroner determined that many of these broader issues weren’t sufficiently connected to each individual death to warrant separate comment under section 25 of the Coroners Act. Instead, the coroner addressed relevant systemic concerns within the findings for each death where they were connected to the specific circumstances.</t>
+*   Therapeutic and sub-therapeutic levels of prescription medicines were detected.
+*   A low level of tetrahydrocannabinol (THC – from cannabis) was found, indicating cannabis use within 24 hours.
+*   The toxicology report also revealed the use of amphetamines, heroin, LSD, and ecstasy intermittently.</t>
+  </si>
+  <si>
+    <t>The coroner addressed general issues related to Graylands Hospital’s systemic problems, primarily concerning the quality of supervision, treatment, and care of the deceased patients. While acknowledging evidence about the hospital’s conditions, the coroner determined that many of these issues weren’t sufficiently connected to each individual death to warrant separate consideration under section 25 of the Coroners Act. Instead, relevant issues were incorporated into the findings for each death where they were directly connected.</t>
+  </si>
+  <si>
+    <t>The provided text does not state whether the coroner made recommendations for future prevention, nor does it detail what those recommendations might have been. The coroner’s approach was to address issues only where they were “sufficiently connected” with the individual deaths and the quality of care.</t>
+  </si>
+  <si>
+    <t>Here’s a differentiation of the immediate cause of death and contributing factors, based on the provided context:
+**Immediate Cause of Death:**
+*   **Ligature Compression of the Neck (Hanging):** This is explicitly stated by Dr. Cooke as the cause of death. The deceased was found suspended by an electrical cord.
+**Contributing Factors:**
+*   **Electrical Cord:** The use of an electrical cord tied to a rafter was the method by which the hanging occurred.
+*   **Unlocked Front Door:** Mr. and Ms. Ward left the front door unlocked, allowing access to the deceased.
+*   **Tetrahydrocannabinol (THC) Use:** The presence of sub-therapeutic levels of THC suggests the deceased was under the influence of cannabis within 24 hours. While not directly causing the hanging, it could have impaired judgment or coordination.
+*   **Potential for Lack of Supervision/Care:** The Coroner notes that issues relating to the deceased’s treatment, supervision and care were considered and addressed in the findings, implying a potential lack of adequate attention to his well-being.
+**In short:** The *immediate cause* was the act of hanging. *Contributing factors* included the means (electrical cord), the unlocked door, and potentially the deceased’s intoxication.</t>
+  </si>
+  <si>
+    <t>Yes, the coroner evaluated the adequacy of supervision, treatment, and care provided.
+Here’s the explanation based on the provided context:
+The coroner specifically addressed the quality of supervision, treatment, and care in several ways:
+*   **Directly commenting on risk assessments:** Paragraph 76 and 77 state that the coroner viewed the risk assessment allowing the deceased unescorted ground access and the decision to grant access as having “no reasonable basis for any criticism.” This indicates a positive evaluation of the treatment team’s approach.
+*   **Acknowledging the ‘least restrictive approach’:** The coroner recognized that the treating team were guided by the need to apply the “least restrictive approach possible” in treatment.
+*   **Addressing impulsivity:** Paragraph 78 notes Dr. Iyyalol’s statement that decisions couldn’t be made without considering the deceased’s impulsivity, implicitly acknowledging a need to balance risk with appropriate treatment.
+In essence, the coroner’s findings demonstrate a review and assessment of the treatment team’s actions and reasoning in relation to the deceased’s care.</t>
+  </si>
+  <si>
+    <t>Yes, this case highlights several broader patterns and lessons relevant to public safety and institutional care. Here’s a breakdown of the key takeaways:
+*   **Systemic Issues at Graylands:** The inquest’s focus on “general or systemic issues” at Graylands is crucial. It suggests deeper problems within the institution – likely relating to staffing levels, building conditions, and perhaps inadequate oversight – that contributed to the deceased’s circumstances and ultimately, his death. This indicates a need for broader scrutiny of similar facilities.
+*   **Risk Assessment Failures:** The case specifically points to a failure in the suicide risk assessment before granting the deceased unescorted ground access. This highlights the importance of thorough risk evaluations, particularly for patients with a history of aggression, manipulation, and attempts to abscond.
+*   **Communication Breakdown:** The reliance on a phone call from a Department of Corrective Services officer demonstrates a lack of integrated communication between different agencies involved in the patient’s care. Improved coordination is essential.
+*   **Lack of Record-Keeping:** The inadequate record-keeping of ground access raises serious concerns about accountability and the ability to track a patient’s movements, increasing the risk of absconding and potential harm.
+*   **Patient Manipulation:** The deceased's behavior – seeking drugs, manipulating the system, and attempting to abscond – reveals a need for institutions to recognize and address manipulative behaviors, as these can be a significant risk factor.
+*   **Overall Institutional Oversight:** The entire situation underscores the importance of robust oversight and quality control within mental health institutions to prevent similar incidents and ensure patient safety.
+In essence, this case isn’t just about one death; it’s a microcosm of potential problems within a system that needs to be constantly evaluated and improved to safeguard vulnerable individuals.</t>
   </si>
 </sst>
 </file>
@@ -503,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -528,10 +582,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -542,10 +596,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -556,10 +610,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -570,10 +624,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -584,10 +638,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -598,10 +652,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -612,10 +666,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -626,10 +680,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -640,10 +694,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -654,10 +708,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -668,10 +722,66 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
